--- a/public/exports-60-250/69116418.xlsx
+++ b/public/exports-60-250/69116418.xlsx
@@ -5404,12 +5404,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205022</t>
+          <t xml:space="preserve">311204999</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786875</t>
+          <t xml:space="preserve">311786872</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
